--- a/artfynd/A 12560-2025 artfynd.xlsx
+++ b/artfynd/A 12560-2025 artfynd.xlsx
@@ -4056,7 +4056,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133059222</v>
+        <v>133059521</v>
       </c>
       <c r="B34" t="n">
         <v>99130</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4099,16 +4099,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Breslätt, Breslätt, Nrk</t>
+          <t>Hällarna, Hällarna, Nrk</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>498964</v>
+        <v>498973</v>
       </c>
       <c r="R34" t="n">
-        <v>6544033</v>
+        <v>6544002</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4149,6 +4151,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4167,7 +4170,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133059428</v>
+        <v>133059222</v>
       </c>
       <c r="B35" t="n">
         <v>99130</v>
@@ -4197,7 +4200,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4216,10 +4219,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>498969</v>
+        <v>498964</v>
       </c>
       <c r="R35" t="n">
-        <v>6544013</v>
+        <v>6544033</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4278,7 +4281,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133059521</v>
+        <v>133059428</v>
       </c>
       <c r="B36" t="n">
         <v>99130</v>
@@ -4308,7 +4311,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4321,18 +4324,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hällarna, Hällarna, Nrk</t>
+          <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>498973</v>
+        <v>498969</v>
       </c>
       <c r="R36" t="n">
-        <v>6544002</v>
+        <v>6544013</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4374,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12560-2025 artfynd.xlsx
+++ b/artfynd/A 12560-2025 artfynd.xlsx
@@ -3252,7 +3252,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133058580</v>
+        <v>133059297</v>
       </c>
       <c r="B27" t="n">
         <v>99130</v>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3290,16 +3290,23 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498987</v>
+        <v>498959</v>
       </c>
       <c r="R27" t="n">
-        <v>6544075</v>
+        <v>6544020</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,51 +3336,37 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>I branten söder om den lilla stigen vid granen som fallit över stigen.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133059297</v>
+        <v>133058580</v>
       </c>
       <c r="B28" t="n">
         <v>99130</v>
@@ -3403,7 +3396,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3411,23 +3404,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498959</v>
+        <v>498987</v>
       </c>
       <c r="R28" t="n">
-        <v>6544020</v>
+        <v>6544075</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3457,30 +3443,44 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>I branten söder om den lilla stigen vid granen som fallit över stigen.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133059521</v>
+        <v>133059222</v>
       </c>
       <c r="B34" t="n">
         <v>99130</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4099,18 +4099,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hällarna, Hällarna, Nrk</t>
+          <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>498973</v>
+        <v>498964</v>
       </c>
       <c r="R34" t="n">
-        <v>6544002</v>
+        <v>6544033</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4151,7 +4149,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4170,7 +4167,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133059222</v>
+        <v>133059428</v>
       </c>
       <c r="B35" t="n">
         <v>99130</v>
@@ -4200,7 +4197,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4219,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>498964</v>
+        <v>498969</v>
       </c>
       <c r="R35" t="n">
-        <v>6544033</v>
+        <v>6544013</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,7 +4278,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133059428</v>
+        <v>133059521</v>
       </c>
       <c r="B36" t="n">
         <v>99130</v>
@@ -4311,7 +4308,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4324,16 +4321,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Breslätt, Breslätt, Nrk</t>
+          <t>Hällarna, Hällarna, Nrk</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>498969</v>
+        <v>498973</v>
       </c>
       <c r="R36" t="n">
-        <v>6544013</v>
+        <v>6544002</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4373,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12560-2025 artfynd.xlsx
+++ b/artfynd/A 12560-2025 artfynd.xlsx
@@ -3252,7 +3252,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133059297</v>
+        <v>133058580</v>
       </c>
       <c r="B27" t="n">
         <v>99130</v>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3290,23 +3290,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498959</v>
+        <v>498987</v>
       </c>
       <c r="R27" t="n">
-        <v>6544020</v>
+        <v>6544075</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,37 +3329,51 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>I branten söder om den lilla stigen vid granen som fallit över stigen.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133058580</v>
+        <v>133059297</v>
       </c>
       <c r="B28" t="n">
         <v>99130</v>
@@ -3396,7 +3403,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3404,16 +3411,23 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498987</v>
+        <v>498959</v>
       </c>
       <c r="R28" t="n">
-        <v>6544075</v>
+        <v>6544020</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3443,44 +3457,30 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>I branten söder om den lilla stigen vid granen som fallit över stigen.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 12560-2025 artfynd.xlsx
+++ b/artfynd/A 12560-2025 artfynd.xlsx
@@ -3022,7 +3022,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133059079</v>
+        <v>133058776</v>
       </c>
       <c r="B25" t="n">
         <v>99130</v>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3065,16 +3065,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498974</v>
+        <v>499010</v>
       </c>
       <c r="R25" t="n">
-        <v>6544031</v>
+        <v>6544042</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3109,12 +3111,18 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Bitvis har många av granarna dött av granbarkborre.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3133,7 +3141,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133058776</v>
+        <v>133059079</v>
       </c>
       <c r="B26" t="n">
         <v>99130</v>
@@ -3163,7 +3171,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3176,18 +3184,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499010</v>
+        <v>498974</v>
       </c>
       <c r="R26" t="n">
-        <v>6544042</v>
+        <v>6544031</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3222,18 +3228,12 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Bitvis har många av granarna dött av granbarkborre.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12560-2025 artfynd.xlsx
+++ b/artfynd/A 12560-2025 artfynd.xlsx
@@ -3022,7 +3022,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133058776</v>
+        <v>133059079</v>
       </c>
       <c r="B25" t="n">
         <v>99130</v>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3065,18 +3065,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499010</v>
+        <v>498974</v>
       </c>
       <c r="R25" t="n">
-        <v>6544042</v>
+        <v>6544031</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3111,18 +3109,12 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Bitvis har många av granarna dött av granbarkborre.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3141,7 +3133,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133059079</v>
+        <v>133058776</v>
       </c>
       <c r="B26" t="n">
         <v>99130</v>
@@ -3171,7 +3163,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3184,16 +3176,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>498974</v>
+        <v>499010</v>
       </c>
       <c r="R26" t="n">
-        <v>6544031</v>
+        <v>6544042</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3228,12 +3222,18 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Bitvis har många av granarna dött av granbarkborre.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12560-2025 artfynd.xlsx
+++ b/artfynd/A 12560-2025 artfynd.xlsx
@@ -3022,10 +3022,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133058776</v>
+        <v>133059079</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3065,18 +3065,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499010</v>
+        <v>498974</v>
       </c>
       <c r="R25" t="n">
-        <v>6544042</v>
+        <v>6544031</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3111,18 +3109,12 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Bitvis har många av granarna dött av granbarkborre.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3141,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133059079</v>
+        <v>133058776</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3171,7 +3163,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3184,16 +3176,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>498974</v>
+        <v>499010</v>
       </c>
       <c r="R26" t="n">
-        <v>6544031</v>
+        <v>6544042</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3228,12 +3222,18 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Bitvis har många av granarna dött av granbarkborre.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>133058580</v>
       </c>
       <c r="B27" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>133059297</v>
       </c>
       <c r="B28" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>133059801</v>
       </c>
       <c r="B29" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>133058928</v>
       </c>
       <c r="B30" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>133058598</v>
       </c>
       <c r="B31" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>133059831</v>
       </c>
       <c r="B32" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>133059616</v>
       </c>
       <c r="B33" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>133059222</v>
       </c>
       <c r="B34" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>133059428</v>
       </c>
       <c r="B35" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>133059521</v>
       </c>
       <c r="B36" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 12560-2025 artfynd.xlsx
+++ b/artfynd/A 12560-2025 artfynd.xlsx
@@ -3025,7 +3025,7 @@
         <v>133059079</v>
       </c>
       <c r="B25" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>133058776</v>
       </c>
       <c r="B26" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>133058580</v>
       </c>
       <c r="B27" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>133059297</v>
       </c>
       <c r="B28" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>133059801</v>
       </c>
       <c r="B29" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>133058928</v>
       </c>
       <c r="B30" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>133058598</v>
       </c>
       <c r="B31" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>133059831</v>
       </c>
       <c r="B32" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>133059616</v>
       </c>
       <c r="B33" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>133059222</v>
       </c>
       <c r="B34" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>133059428</v>
       </c>
       <c r="B35" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>133059521</v>
       </c>
       <c r="B36" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 12560-2025 artfynd.xlsx
+++ b/artfynd/A 12560-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112439096</v>
+        <v>112439078</v>
       </c>
       <c r="B2" t="n">
-        <v>99098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498916</v>
+        <v>499005</v>
       </c>
       <c r="R2" t="n">
-        <v>6543985</v>
+        <v>6544047</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112439081</v>
+        <v>112439087</v>
       </c>
       <c r="B3" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499021</v>
+        <v>498956</v>
       </c>
       <c r="R3" t="n">
-        <v>6544034</v>
+        <v>6544029</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112439102</v>
+        <v>112439095</v>
       </c>
       <c r="B4" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498876</v>
+        <v>498927</v>
       </c>
       <c r="R4" t="n">
-        <v>6544008</v>
+        <v>6543978</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112439085</v>
+        <v>112439093</v>
       </c>
       <c r="B5" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498966</v>
+        <v>498926</v>
       </c>
       <c r="R5" t="n">
-        <v>6544028</v>
+        <v>6543980</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1045,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,37 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112439095</v>
+        <v>112439080</v>
       </c>
       <c r="B6" t="n">
-        <v>89653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498927</v>
+        <v>499029</v>
       </c>
       <c r="R6" t="n">
-        <v>6543978</v>
+        <v>6544035</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112439093</v>
+        <v>112439077</v>
       </c>
       <c r="B7" t="n">
-        <v>90055</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5321</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498926</v>
+        <v>499016</v>
       </c>
       <c r="R7" t="n">
-        <v>6543980</v>
+        <v>6544060</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,7 +1240,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1288,15 +1258,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112439100</v>
+        <v>112439071</v>
       </c>
       <c r="B8" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498910</v>
+        <v>498763</v>
       </c>
       <c r="R8" t="n">
-        <v>6543984</v>
+        <v>6544097</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,12 +1358,7 @@
         <v>112439072</v>
       </c>
       <c r="B9" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,7 +1390,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498807</v>
+        <v>498808</v>
       </c>
       <c r="R9" t="n">
         <v>6544078</v>
@@ -1495,12 +1455,7 @@
         <v>112439073</v>
       </c>
       <c r="B10" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,7 +1487,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498834</v>
+        <v>498833</v>
       </c>
       <c r="R10" t="n">
         <v>6544085</v>
@@ -1594,37 +1549,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112439087</v>
+        <v>112439074</v>
       </c>
       <c r="B11" t="n">
-        <v>89653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498956</v>
+        <v>498859</v>
       </c>
       <c r="R11" t="n">
-        <v>6544029</v>
+        <v>6544117</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,15 +1646,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112439090</v>
+        <v>112439075</v>
       </c>
       <c r="B12" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498970</v>
+        <v>499004</v>
       </c>
       <c r="R12" t="n">
-        <v>6544002</v>
+        <v>6544079</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,15 +1743,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112439088</v>
+        <v>112439081</v>
       </c>
       <c r="B13" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498975</v>
+        <v>499021</v>
       </c>
       <c r="R13" t="n">
-        <v>6544015</v>
+        <v>6544034</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,15 +1840,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112439084</v>
+        <v>112439082</v>
       </c>
       <c r="B14" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498984</v>
+        <v>499001</v>
       </c>
       <c r="R14" t="n">
-        <v>6544038</v>
+        <v>6544031</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,37 +1937,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112439077</v>
+        <v>112439084</v>
       </c>
       <c r="B15" t="n">
-        <v>56656</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2042,10 +1972,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499016</v>
+        <v>498984</v>
       </c>
       <c r="R15" t="n">
-        <v>6544060</v>
+        <v>6544038</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,15 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112439101</v>
+        <v>112439085</v>
       </c>
       <c r="B16" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2144,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498877</v>
+        <v>498966</v>
       </c>
       <c r="R16" t="n">
-        <v>6543986</v>
+        <v>6544029</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,37 +2131,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112439078</v>
+        <v>112439088</v>
       </c>
       <c r="B17" t="n">
-        <v>89653</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2246,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499005</v>
+        <v>498975</v>
       </c>
       <c r="R17" t="n">
-        <v>6544047</v>
+        <v>6544015</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,15 +2228,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112439071</v>
+        <v>112439090</v>
       </c>
       <c r="B18" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498764</v>
+        <v>498970</v>
       </c>
       <c r="R18" t="n">
-        <v>6544097</v>
+        <v>6544001</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,12 +2328,7 @@
         <v>112439091</v>
       </c>
       <c r="B19" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2450,7 +2360,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498934</v>
+        <v>498933</v>
       </c>
       <c r="R19" t="n">
         <v>6543995</v>
@@ -2512,15 +2422,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112439082</v>
+        <v>112439094</v>
       </c>
       <c r="B20" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2552,10 +2457,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499001</v>
+        <v>498927</v>
       </c>
       <c r="R20" t="n">
-        <v>6544031</v>
+        <v>6543978</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2614,15 +2519,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112439104</v>
+        <v>112439100</v>
       </c>
       <c r="B21" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2654,10 +2554,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498839</v>
+        <v>498911</v>
       </c>
       <c r="R21" t="n">
-        <v>6544020</v>
+        <v>6543984</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2716,15 +2616,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112439074</v>
+        <v>112439101</v>
       </c>
       <c r="B22" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2756,10 +2651,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498859</v>
+        <v>498877</v>
       </c>
       <c r="R22" t="n">
-        <v>6544117</v>
+        <v>6543985</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,15 +2713,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112439075</v>
+        <v>112439102</v>
       </c>
       <c r="B23" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,10 +2748,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499003</v>
+        <v>498876</v>
       </c>
       <c r="R23" t="n">
-        <v>6544079</v>
+        <v>6544009</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,15 +2810,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112439094</v>
+        <v>112439104</v>
       </c>
       <c r="B24" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2960,10 +2845,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498927</v>
+        <v>498839</v>
       </c>
       <c r="R24" t="n">
-        <v>6543978</v>
+        <v>6544020</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,10 +2907,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133059079</v>
+        <v>133058580</v>
       </c>
       <c r="B25" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3052,7 +2937,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3060,21 +2945,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498974</v>
+        <v>498987</v>
       </c>
       <c r="R25" t="n">
-        <v>6544031</v>
+        <v>6544075</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3104,9 +2984,24 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I branten söder om den lilla stigen vid granen som fallit över stigen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3121,22 +3016,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133058776</v>
+        <v>133058598</v>
       </c>
       <c r="B26" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3058,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3171,23 +3066,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499010</v>
+        <v>498980</v>
       </c>
       <c r="R26" t="n">
-        <v>6544042</v>
+        <v>6544074</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,14 +3105,19 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Bitvis har många av granarna dött av granbarkborre.</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3233,29 +3126,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133058580</v>
+        <v>133058776</v>
       </c>
       <c r="B27" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3282,7 +3174,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3290,16 +3182,23 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498987</v>
+        <v>499010</v>
       </c>
       <c r="R27" t="n">
-        <v>6544075</v>
+        <v>6544042</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,24 +3228,14 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I branten söder om den lilla stigen vid granen som fallit över stigen.</t>
+          <t>Barrnaturskog. Bitvis har många av granarna dött av granbarkborre.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3355,28 +3244,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133059297</v>
+        <v>133058928</v>
       </c>
       <c r="B28" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3403,7 +3293,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3424,10 +3314,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498959</v>
+        <v>499007</v>
       </c>
       <c r="R28" t="n">
-        <v>6544020</v>
+        <v>6544038</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3487,10 +3377,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133059801</v>
+        <v>133059079</v>
       </c>
       <c r="B29" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3517,7 +3407,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3530,18 +3420,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498918</v>
+        <v>498974</v>
       </c>
       <c r="R29" t="n">
-        <v>6544058</v>
+        <v>6544031</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,7 +3470,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3601,10 +3488,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133058928</v>
+        <v>133059222</v>
       </c>
       <c r="B30" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3631,7 +3518,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3644,18 +3531,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499007</v>
+        <v>498964</v>
       </c>
       <c r="R30" t="n">
-        <v>6544038</v>
+        <v>6544033</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3696,7 +3581,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3715,10 +3599,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133058598</v>
+        <v>133059297</v>
       </c>
       <c r="B31" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3745,7 +3629,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3753,16 +3637,23 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>498980</v>
+        <v>498959</v>
       </c>
       <c r="R31" t="n">
-        <v>6544074</v>
+        <v>6544020</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3792,49 +3683,40 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133059831</v>
+        <v>133059428</v>
       </c>
       <c r="B32" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3861,7 +3743,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3874,18 +3756,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>498920</v>
+        <v>498969</v>
       </c>
       <c r="R32" t="n">
-        <v>6544063</v>
+        <v>6544013</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3926,7 +3806,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3945,10 +3824,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133059616</v>
+        <v>133059521</v>
       </c>
       <c r="B33" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3975,7 +3854,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3988,16 +3867,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Breslätt, Breslätt, Nrk</t>
+          <t>Hällarna, Hällarna, Nrk</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>498959</v>
+        <v>498973</v>
       </c>
       <c r="R33" t="n">
-        <v>6544006</v>
+        <v>6544002</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4038,6 +3919,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4056,10 +3938,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133059222</v>
+        <v>133059616</v>
       </c>
       <c r="B34" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4086,7 +3968,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4105,10 +3987,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>498964</v>
+        <v>498959</v>
       </c>
       <c r="R34" t="n">
-        <v>6544033</v>
+        <v>6544006</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,10 +4049,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133059428</v>
+        <v>133059801</v>
       </c>
       <c r="B35" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4197,7 +4079,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4210,16 +4092,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>498969</v>
+        <v>498918</v>
       </c>
       <c r="R35" t="n">
-        <v>6544013</v>
+        <v>6544058</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,6 +4144,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4278,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133059521</v>
+        <v>133059831</v>
       </c>
       <c r="B36" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4308,7 +4193,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4325,14 +4210,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hällarna, Hällarna, Nrk</t>
+          <t>Breslätt, Breslätt, Nrk</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>498973</v>
+        <v>498920</v>
       </c>
       <c r="R36" t="n">
-        <v>6544002</v>
+        <v>6544063</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4389,6 +4274,103 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>112439096</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Östansjö, Nrk</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>498916</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6543985</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12560-2025 artfynd.xlsx
+++ b/artfynd/A 12560-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439078</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439087</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439095</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439093</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439080</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439077</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439071</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439072</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439073</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439074</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439075</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439081</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,6 +1999,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439082</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2031,6 +2101,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439084</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2128,6 +2203,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439085</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2225,6 +2305,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439088</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2322,6 +2407,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439090</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2419,6 +2509,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439091</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2516,6 +2611,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439094</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2613,6 +2713,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439100</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2710,6 +2815,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439101</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2807,6 +2917,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439102</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2904,6 +3019,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439104</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3025,6 +3145,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133058580</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3141,6 +3266,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133058598</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3260,6 +3390,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133058776</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3374,6 +3509,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133058928</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3485,6 +3625,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059079</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3596,6 +3741,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059222</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3710,6 +3860,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059297</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3821,6 +3976,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059428</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3935,6 +4095,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059521</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4046,6 +4211,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059616</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4160,6 +4330,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059801</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4274,6 +4449,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059831</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4371,8 +4551,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439096</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>